--- a/output/2026_A24_SECCION_E_TABLAS.xlsx
+++ b/output/2026_A24_SECCION_E_TABLAS.xlsx
@@ -78,7 +78,7 @@
     <t>Servicio de Salud Metropolitano Sur</t>
   </si>
   <si>
-    <t>Servicio de Salud Metropolitano Sur Oriente</t>
+    <t>Servicio de Salud Metropolitano Sur - Oriente</t>
   </si>
   <si>
     <t>nombre_comuna</t>
@@ -562,40 +562,40 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>10733</v>
+        <v>16811</v>
       </c>
       <c r="C2">
-        <v>7848</v>
+        <v>12096</v>
       </c>
       <c r="D2">
-        <v>1242</v>
+        <v>1992</v>
       </c>
       <c r="E2">
-        <v>9090</v>
+        <v>14088</v>
       </c>
       <c r="F2">
-        <v>1522</v>
+        <v>2501</v>
       </c>
       <c r="G2">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I2">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>236</v>
+        <v>385</v>
       </c>
       <c r="L2" s="1">
-        <v>0.731202832386099</v>
+        <v>0.7195288799000654</v>
       </c>
       <c r="M2" s="1">
-        <v>0.8469207118233486</v>
+        <v>0.8380227232169413</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -603,19 +603,19 @@
         <v>14</v>
       </c>
       <c r="B3">
-        <v>1619</v>
+        <v>2625</v>
       </c>
       <c r="C3">
-        <v>935</v>
+        <v>1544</v>
       </c>
       <c r="D3">
-        <v>305</v>
+        <v>450</v>
       </c>
       <c r="E3">
-        <v>1240</v>
+        <v>1994</v>
       </c>
       <c r="F3">
-        <v>346</v>
+        <v>563</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -624,7 +624,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -633,10 +633,10 @@
         <v>1</v>
       </c>
       <c r="L3" s="1">
-        <v>0.5775169857936998</v>
+        <v>0.5881904761904762</v>
       </c>
       <c r="M3" s="1">
-        <v>0.7659048795552811</v>
+        <v>0.7596190476190476</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -644,40 +644,40 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>2386</v>
+        <v>3564</v>
       </c>
       <c r="C4">
-        <v>1851</v>
+        <v>2753</v>
       </c>
       <c r="D4">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="E4">
-        <v>1990</v>
+        <v>2950</v>
       </c>
       <c r="F4">
-        <v>295</v>
+        <v>492</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="L4" s="1">
-        <v>0.7757753562447611</v>
+        <v>0.7724466891133558</v>
       </c>
       <c r="M4" s="1">
-        <v>0.8340318524727578</v>
+        <v>0.8277216610549943</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -685,25 +685,25 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>1762</v>
+        <v>2820</v>
       </c>
       <c r="C5">
-        <v>1187</v>
+        <v>1867</v>
       </c>
       <c r="D5">
-        <v>420</v>
+        <v>689</v>
       </c>
       <c r="E5">
-        <v>1607</v>
+        <v>2556</v>
       </c>
       <c r="F5">
-        <v>138</v>
+        <v>233</v>
       </c>
       <c r="G5">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -712,13 +712,13 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L5" s="1">
-        <v>0.6736662883087401</v>
+        <v>0.6620567375886525</v>
       </c>
       <c r="M5" s="1">
-        <v>0.9120317820658342</v>
+        <v>0.9063829787234042</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -726,19 +726,19 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>1013</v>
+        <v>1566</v>
       </c>
       <c r="C6">
-        <v>745</v>
+        <v>1108</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="E6">
-        <v>775</v>
+        <v>1186</v>
       </c>
       <c r="F6">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -747,19 +747,19 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>126</v>
+        <v>222</v>
       </c>
       <c r="L6" s="1">
-        <v>0.7354392892398816</v>
+        <v>0.7075351213282248</v>
       </c>
       <c r="M6" s="1">
-        <v>0.7650542941757157</v>
+        <v>0.7573435504469987</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -767,40 +767,40 @@
         <v>18</v>
       </c>
       <c r="B7">
-        <v>2061</v>
+        <v>3252</v>
       </c>
       <c r="C7">
-        <v>1782</v>
+        <v>2786</v>
       </c>
       <c r="D7">
-        <v>107</v>
+        <v>235</v>
       </c>
       <c r="E7">
-        <v>1889</v>
+        <v>3021</v>
       </c>
       <c r="F7">
-        <v>246</v>
+        <v>389</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H7">
         <v>2</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="L7" s="1">
-        <v>0.8646288209606987</v>
+        <v>0.8567035670356704</v>
       </c>
       <c r="M7" s="1">
-        <v>0.9165453663270258</v>
+        <v>0.9289667896678967</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -808,40 +808,40 @@
         <v>19</v>
       </c>
       <c r="B8">
-        <v>1892</v>
+        <v>2984</v>
       </c>
       <c r="C8">
-        <v>1348</v>
+        <v>2038</v>
       </c>
       <c r="D8">
-        <v>241</v>
+        <v>343</v>
       </c>
       <c r="E8">
-        <v>1589</v>
+        <v>2381</v>
       </c>
       <c r="F8">
-        <v>387</v>
+        <v>670</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L8" s="1">
-        <v>0.7124735729386892</v>
+        <v>0.6829758713136729</v>
       </c>
       <c r="M8" s="1">
-        <v>0.8398520084566596</v>
+        <v>0.7979222520107239</v>
       </c>
     </row>
   </sheetData>
@@ -903,40 +903,40 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>2901</v>
+        <v>4701</v>
       </c>
       <c r="C2">
-        <v>86</v>
+        <v>163</v>
       </c>
       <c r="D2">
-        <v>823</v>
+        <v>1377</v>
       </c>
       <c r="E2">
-        <v>909</v>
+        <v>1540</v>
       </c>
       <c r="F2">
-        <v>1692</v>
+        <v>2735</v>
       </c>
       <c r="G2">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="H2">
-        <v>173</v>
+        <v>257</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L2" s="1">
-        <v>0.02964495001723544</v>
+        <v>0.03467347372899383</v>
       </c>
       <c r="M2" s="1">
-        <v>0.3133402275077559</v>
+        <v>0.3275898744947883</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -944,28 +944,28 @@
         <v>14</v>
       </c>
       <c r="B3">
-        <v>424</v>
+        <v>677</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>152</v>
+        <v>230</v>
       </c>
       <c r="E3">
-        <v>153</v>
+        <v>232</v>
       </c>
       <c r="F3">
-        <v>233</v>
+        <v>387</v>
       </c>
       <c r="G3">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H3">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -974,10 +974,10 @@
         <v>1</v>
       </c>
       <c r="L3" s="1">
-        <v>0.002358490566037736</v>
+        <v>0.002954209748892172</v>
       </c>
       <c r="M3" s="1">
-        <v>0.3608490566037736</v>
+        <v>0.3426883308714919</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -985,28 +985,28 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>309</v>
+        <v>446</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D4">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="E4">
-        <v>116</v>
+        <v>175</v>
       </c>
       <c r="F4">
-        <v>167</v>
+        <v>229</v>
       </c>
       <c r="G4">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="H4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="L4" s="1">
-        <v>0.1067961165048544</v>
+        <v>0.1322869955156951</v>
       </c>
       <c r="M4" s="1">
-        <v>0.3754045307443366</v>
+        <v>0.3923766816143498</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1026,28 +1026,28 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>455</v>
+        <v>749</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>115</v>
+        <v>158</v>
       </c>
       <c r="E5">
-        <v>115</v>
+        <v>158</v>
       </c>
       <c r="F5">
-        <v>290</v>
+        <v>505</v>
       </c>
       <c r="G5">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H5">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="1">
-        <v>0.2527472527472527</v>
+        <v>0.2109479305740988</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1067,25 +1067,25 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>380</v>
+        <v>616</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D6">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="E6">
-        <v>96</v>
+        <v>151</v>
       </c>
       <c r="F6">
-        <v>267</v>
+        <v>441</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1097,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>0.03947368421052631</v>
+        <v>0.03733766233766234</v>
       </c>
       <c r="M6" s="1">
-        <v>0.2526315789473684</v>
+        <v>0.2451298701298701</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1108,40 +1108,40 @@
         <v>18</v>
       </c>
       <c r="B7">
-        <v>505</v>
+        <v>876</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D7">
-        <v>48</v>
+        <v>128</v>
       </c>
       <c r="E7">
-        <v>57</v>
+        <v>152</v>
       </c>
       <c r="F7">
-        <v>381</v>
+        <v>654</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H7">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" s="1">
-        <v>0.01782178217821782</v>
+        <v>0.0273972602739726</v>
       </c>
       <c r="M7" s="1">
-        <v>0.1128712871287129</v>
+        <v>0.1735159817351598</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1149,40 +1149,40 @@
         <v>19</v>
       </c>
       <c r="B8">
-        <v>828</v>
+        <v>1337</v>
       </c>
       <c r="C8">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="D8">
-        <v>344</v>
+        <v>617</v>
       </c>
       <c r="E8">
-        <v>372</v>
+        <v>672</v>
       </c>
       <c r="F8">
-        <v>354</v>
+        <v>519</v>
       </c>
       <c r="G8">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H8">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L8" s="1">
-        <v>0.03381642512077294</v>
+        <v>0.04113687359760658</v>
       </c>
       <c r="M8" s="1">
-        <v>0.4492753623188406</v>
+        <v>0.5026178010471204</v>
       </c>
     </row>
   </sheetData>
@@ -1244,40 +1244,40 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>10733</v>
+        <v>16811</v>
       </c>
       <c r="C2">
-        <v>7848</v>
+        <v>12096</v>
       </c>
       <c r="D2">
-        <v>1242</v>
+        <v>1992</v>
       </c>
       <c r="E2">
-        <v>9090</v>
+        <v>14088</v>
       </c>
       <c r="F2">
-        <v>1522</v>
+        <v>2501</v>
       </c>
       <c r="G2">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I2">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>236</v>
+        <v>385</v>
       </c>
       <c r="L2" s="1">
-        <v>0.731202832386099</v>
+        <v>0.7195288799000654</v>
       </c>
       <c r="M2" s="1">
-        <v>0.8469207118233486</v>
+        <v>0.8380227232169413</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1285,22 +1285,22 @@
         <v>21</v>
       </c>
       <c r="B3">
-        <v>275</v>
+        <v>431</v>
       </c>
       <c r="C3">
-        <v>239</v>
+        <v>381</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>255</v>
+        <v>404</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -1315,10 +1315,10 @@
         <v>0</v>
       </c>
       <c r="L3" s="1">
-        <v>0.8690909090909091</v>
+        <v>0.8839907192575406</v>
       </c>
       <c r="M3" s="1">
-        <v>0.9272727272727272</v>
+        <v>0.9373549883990719</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1326,22 +1326,22 @@
         <v>22</v>
       </c>
       <c r="B4">
-        <v>902</v>
+        <v>1423</v>
       </c>
       <c r="C4">
-        <v>791</v>
+        <v>1235</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>791</v>
+        <v>1235</v>
       </c>
       <c r="F4">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1356,10 +1356,10 @@
         <v>0</v>
       </c>
       <c r="L4" s="1">
-        <v>0.876940133037694</v>
+        <v>0.8678847505270555</v>
       </c>
       <c r="M4" s="1">
-        <v>0.876940133037694</v>
+        <v>0.8678847505270555</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1367,19 +1367,19 @@
         <v>23</v>
       </c>
       <c r="B5">
-        <v>1619</v>
+        <v>2625</v>
       </c>
       <c r="C5">
-        <v>935</v>
+        <v>1544</v>
       </c>
       <c r="D5">
-        <v>305</v>
+        <v>450</v>
       </c>
       <c r="E5">
-        <v>1240</v>
+        <v>1994</v>
       </c>
       <c r="F5">
-        <v>346</v>
+        <v>563</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1388,7 +1388,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1397,10 +1397,10 @@
         <v>1</v>
       </c>
       <c r="L5" s="1">
-        <v>0.5775169857936998</v>
+        <v>0.5881904761904762</v>
       </c>
       <c r="M5" s="1">
-        <v>0.7659048795552811</v>
+        <v>0.7596190476190476</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1408,19 +1408,19 @@
         <v>24</v>
       </c>
       <c r="B6">
-        <v>773</v>
+        <v>1223</v>
       </c>
       <c r="C6">
-        <v>611</v>
+        <v>920</v>
       </c>
       <c r="D6">
         <v>124</v>
       </c>
       <c r="E6">
-        <v>735</v>
+        <v>1044</v>
       </c>
       <c r="F6">
-        <v>158</v>
+        <v>295</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1429,19 +1429,19 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="1">
-        <v>0.7904269081500647</v>
+        <v>0.7522485690923958</v>
       </c>
       <c r="M6" s="1">
-        <v>0.9508408796895214</v>
+        <v>0.8536385936222404</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1449,22 +1449,22 @@
         <v>25</v>
       </c>
       <c r="B7">
-        <v>753</v>
+        <v>1194</v>
       </c>
       <c r="C7">
-        <v>573</v>
+        <v>902</v>
       </c>
       <c r="D7">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="E7">
-        <v>639</v>
+        <v>1005</v>
       </c>
       <c r="F7">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1476,13 +1476,13 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L7" s="1">
-        <v>0.7609561752988048</v>
+        <v>0.7554438860971524</v>
       </c>
       <c r="M7" s="1">
-        <v>0.8486055776892431</v>
+        <v>0.8417085427135679</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1490,19 +1490,19 @@
         <v>26</v>
       </c>
       <c r="B8">
-        <v>357</v>
+        <v>548</v>
       </c>
       <c r="C8">
-        <v>345</v>
+        <v>509</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E8">
-        <v>345</v>
+        <v>520</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1520,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="L8" s="1">
-        <v>0.9663865546218487</v>
+        <v>0.9288321167883211</v>
       </c>
       <c r="M8" s="1">
-        <v>0.9663865546218487</v>
+        <v>0.948905109489051</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1531,19 +1531,19 @@
         <v>27</v>
       </c>
       <c r="B9">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C9">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1561,10 +1561,10 @@
         <v>0</v>
       </c>
       <c r="L9" s="1">
-        <v>0.9583333333333334</v>
+        <v>0.9130434782608695</v>
       </c>
       <c r="M9" s="1">
-        <v>1</v>
+        <v>0.9565217391304348</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1572,19 +1572,19 @@
         <v>28</v>
       </c>
       <c r="B10">
-        <v>1013</v>
+        <v>1566</v>
       </c>
       <c r="C10">
-        <v>745</v>
+        <v>1108</v>
       </c>
       <c r="D10">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="E10">
-        <v>775</v>
+        <v>1186</v>
       </c>
       <c r="F10">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1593,19 +1593,19 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>126</v>
+        <v>222</v>
       </c>
       <c r="L10" s="1">
-        <v>0.7354392892398816</v>
+        <v>0.7075351213282248</v>
       </c>
       <c r="M10" s="1">
-        <v>0.7650542941757157</v>
+        <v>0.7573435504469987</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1613,40 +1613,40 @@
         <v>29</v>
       </c>
       <c r="B11">
-        <v>951</v>
+        <v>1469</v>
       </c>
       <c r="C11">
-        <v>674</v>
+        <v>1003</v>
       </c>
       <c r="D11">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="E11">
-        <v>729</v>
+        <v>1116</v>
       </c>
       <c r="F11">
-        <v>205</v>
+        <v>323</v>
       </c>
       <c r="G11">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L11" s="1">
-        <v>0.7087276550998949</v>
+        <v>0.6827773995915589</v>
       </c>
       <c r="M11" s="1">
-        <v>0.7665615141955836</v>
+        <v>0.7597004765146358</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1654,19 +1654,19 @@
         <v>30</v>
       </c>
       <c r="B12">
-        <v>952</v>
+        <v>1473</v>
       </c>
       <c r="C12">
-        <v>783</v>
+        <v>1156</v>
       </c>
       <c r="D12">
-        <v>67</v>
+        <v>170</v>
       </c>
       <c r="E12">
-        <v>850</v>
+        <v>1326</v>
       </c>
       <c r="F12">
-        <v>200</v>
+        <v>323</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1681,13 +1681,13 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="1">
-        <v>0.8224789915966386</v>
+        <v>0.7847929395790902</v>
       </c>
       <c r="M12" s="1">
-        <v>0.8928571428571429</v>
+        <v>0.90020366598778</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1695,40 +1695,40 @@
         <v>31</v>
       </c>
       <c r="B13">
-        <v>834</v>
+        <v>1348</v>
       </c>
       <c r="C13">
-        <v>760</v>
+        <v>1249</v>
       </c>
       <c r="D13">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="E13">
-        <v>784</v>
+        <v>1291</v>
       </c>
       <c r="F13">
+        <v>38</v>
+      </c>
+      <c r="G13">
+        <v>16</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>15</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
         <v>30</v>
       </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>8</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>18</v>
-      </c>
       <c r="L13" s="1">
-        <v>0.9112709832134293</v>
+        <v>0.9265578635014837</v>
       </c>
       <c r="M13" s="1">
-        <v>0.9400479616306955</v>
+        <v>0.9577151335311572</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1736,19 +1736,19 @@
         <v>32</v>
       </c>
       <c r="B14">
-        <v>168</v>
+        <v>292</v>
       </c>
       <c r="C14">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="D14">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="E14">
-        <v>125</v>
+        <v>221</v>
       </c>
       <c r="F14">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1766,10 +1766,10 @@
         <v>0</v>
       </c>
       <c r="L14" s="1">
-        <v>0.375</v>
+        <v>0.3938356164383562</v>
       </c>
       <c r="M14" s="1">
-        <v>0.7440476190476191</v>
+        <v>0.7568493150684932</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1777,40 +1777,40 @@
         <v>33</v>
       </c>
       <c r="B15">
-        <v>1750</v>
+        <v>2635</v>
       </c>
       <c r="C15">
-        <v>992</v>
+        <v>1475</v>
       </c>
       <c r="D15">
-        <v>491</v>
+        <v>769</v>
       </c>
       <c r="E15">
-        <v>1483</v>
+        <v>2244</v>
       </c>
       <c r="F15">
-        <v>175</v>
+        <v>274</v>
       </c>
       <c r="G15">
+        <v>31</v>
+      </c>
+      <c r="H15">
         <v>4</v>
       </c>
-      <c r="H15">
-        <v>2</v>
-      </c>
       <c r="I15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="L15" s="1">
-        <v>0.5668571428571428</v>
+        <v>0.5597722960151803</v>
       </c>
       <c r="M15" s="1">
-        <v>0.8474285714285714</v>
+        <v>0.8516129032258064</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1818,25 +1818,25 @@
         <v>34</v>
       </c>
       <c r="B16">
-        <v>362</v>
+        <v>538</v>
       </c>
       <c r="C16">
-        <v>314</v>
+        <v>457</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16">
-        <v>315</v>
+        <v>458</v>
       </c>
       <c r="F16">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1845,13 +1845,13 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L16" s="1">
-        <v>0.8674033149171271</v>
+        <v>0.8494423791821561</v>
       </c>
       <c r="M16" s="1">
-        <v>0.8701657458563536</v>
+        <v>0.8513011152416357</v>
       </c>
     </row>
   </sheetData>
@@ -1913,40 +1913,40 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>2901</v>
+        <v>4701</v>
       </c>
       <c r="C2">
-        <v>86</v>
+        <v>163</v>
       </c>
       <c r="D2">
-        <v>823</v>
+        <v>1377</v>
       </c>
       <c r="E2">
-        <v>909</v>
+        <v>1540</v>
       </c>
       <c r="F2">
-        <v>1692</v>
+        <v>2735</v>
       </c>
       <c r="G2">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="H2">
-        <v>173</v>
+        <v>257</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L2" s="1">
-        <v>0.02964495001723544</v>
+        <v>0.03467347372899383</v>
       </c>
       <c r="M2" s="1">
-        <v>0.3133402275077559</v>
+        <v>0.3275898744947883</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1954,25 +1954,25 @@
         <v>21</v>
       </c>
       <c r="B3">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1984,10 +1984,10 @@
         <v>0</v>
       </c>
       <c r="L3" s="1">
-        <v>0.08</v>
+        <v>0.1022727272727273</v>
       </c>
       <c r="M3" s="1">
-        <v>0.36</v>
+        <v>0.4204545454545455</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2030,28 +2030,28 @@
         <v>23</v>
       </c>
       <c r="B5">
-        <v>424</v>
+        <v>677</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>152</v>
+        <v>230</v>
       </c>
       <c r="E5">
-        <v>153</v>
+        <v>232</v>
       </c>
       <c r="F5">
-        <v>233</v>
+        <v>387</v>
       </c>
       <c r="G5">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H5">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2060,10 +2060,10 @@
         <v>1</v>
       </c>
       <c r="L5" s="1">
-        <v>0.002358490566037736</v>
+        <v>0.002954209748892172</v>
       </c>
       <c r="M5" s="1">
-        <v>0.3608490566037736</v>
+        <v>0.3426883308714919</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2071,25 +2071,25 @@
         <v>24</v>
       </c>
       <c r="B6">
-        <v>165</v>
+        <v>244</v>
       </c>
       <c r="C6">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D6">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="E6">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="F6">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -2101,10 +2101,10 @@
         <v>4</v>
       </c>
       <c r="L6" s="1">
-        <v>0.1575757575757576</v>
+        <v>0.2172131147540984</v>
       </c>
       <c r="M6" s="1">
-        <v>0.5757575757575758</v>
+        <v>0.610655737704918</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2112,25 +2112,25 @@
         <v>25</v>
       </c>
       <c r="B7">
-        <v>198</v>
+        <v>344</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F7">
-        <v>147</v>
+        <v>272</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="1">
-        <v>0.1868686868686869</v>
+        <v>0.1279069767441861</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2153,22 +2153,22 @@
         <v>26</v>
       </c>
       <c r="B8">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="C8">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D8">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="E8">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
         <v>4</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
       </c>
       <c r="H8">
         <v>5</v>
@@ -2183,10 +2183,10 @@
         <v>0</v>
       </c>
       <c r="L8" s="1">
-        <v>0.358695652173913</v>
+        <v>0.4068965517241379</v>
       </c>
       <c r="M8" s="1">
-        <v>0.9565217391304348</v>
+        <v>0.8896551724137931</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2229,25 +2229,25 @@
         <v>28</v>
       </c>
       <c r="B10">
-        <v>380</v>
+        <v>616</v>
       </c>
       <c r="C10">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D10">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="E10">
-        <v>96</v>
+        <v>151</v>
       </c>
       <c r="F10">
-        <v>267</v>
+        <v>441</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -2259,10 +2259,10 @@
         <v>0</v>
       </c>
       <c r="L10" s="1">
-        <v>0.03947368421052631</v>
+        <v>0.03733766233766234</v>
       </c>
       <c r="M10" s="1">
-        <v>0.2526315789473684</v>
+        <v>0.2451298701298701</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2270,19 +2270,19 @@
         <v>29</v>
       </c>
       <c r="B11">
-        <v>424</v>
+        <v>708</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>151</v>
+        <v>306</v>
       </c>
       <c r="E11">
-        <v>151</v>
+        <v>306</v>
       </c>
       <c r="F11">
-        <v>210</v>
+        <v>292</v>
       </c>
       <c r="G11">
         <v>7</v>
@@ -2291,7 +2291,7 @@
         <v>7</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="1">
-        <v>0.3561320754716981</v>
+        <v>0.4322033898305085</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -2311,25 +2311,25 @@
         <v>30</v>
       </c>
       <c r="B12">
-        <v>256</v>
+        <v>429</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D12">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="E12">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="F12">
-        <v>205</v>
+        <v>347</v>
       </c>
       <c r="G12">
         <v>1</v>
       </c>
       <c r="H12">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2341,10 +2341,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="1">
-        <v>0.01953125</v>
+        <v>0.02797202797202797</v>
       </c>
       <c r="M12" s="1">
-        <v>0.1015625</v>
+        <v>0.2191142191142191</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -2352,40 +2352,40 @@
         <v>31</v>
       </c>
       <c r="B13">
-        <v>199</v>
+        <v>359</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D13">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E13">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F13">
-        <v>150</v>
+        <v>261</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H13">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L13" s="1">
-        <v>0</v>
+        <v>0.008356545961002786</v>
       </c>
       <c r="M13" s="1">
-        <v>0.06532663316582915</v>
+        <v>0.0584958217270195</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -2393,40 +2393,40 @@
         <v>32</v>
       </c>
       <c r="B14">
-        <v>239</v>
+        <v>385</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14">
-        <v>124</v>
+        <v>215</v>
       </c>
       <c r="E14">
-        <v>126</v>
+        <v>217</v>
       </c>
       <c r="F14">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L14" s="1">
-        <v>0.008368200836820083</v>
+        <v>0.005194805194805195</v>
       </c>
       <c r="M14" s="1">
-        <v>0.5271966527196653</v>
+        <v>0.5636363636363636</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -2434,28 +2434,28 @@
         <v>33</v>
       </c>
       <c r="B15">
-        <v>435</v>
+        <v>649</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>101</v>
+        <v>151</v>
       </c>
       <c r="E15">
-        <v>101</v>
+        <v>151</v>
       </c>
       <c r="F15">
-        <v>276</v>
+        <v>413</v>
       </c>
       <c r="G15">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="H15">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2467,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="1">
-        <v>0.232183908045977</v>
+        <v>0.2326656394453005</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -2475,19 +2475,19 @@
         <v>34</v>
       </c>
       <c r="B16">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F16">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2508,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="1">
-        <v>0.1282051282051282</v>
+        <v>0.1578947368421053</v>
       </c>
     </row>
   </sheetData>
@@ -2570,40 +2570,40 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>10733</v>
+        <v>16811</v>
       </c>
       <c r="C2">
-        <v>7848</v>
+        <v>12096</v>
       </c>
       <c r="D2">
-        <v>1242</v>
+        <v>1992</v>
       </c>
       <c r="E2">
-        <v>9090</v>
+        <v>14088</v>
       </c>
       <c r="F2">
-        <v>1522</v>
+        <v>2501</v>
       </c>
       <c r="G2">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I2">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>236</v>
+        <v>385</v>
       </c>
       <c r="L2" s="1">
-        <v>0.731202832386099</v>
+        <v>0.7195288799000654</v>
       </c>
       <c r="M2" s="1">
-        <v>0.8469207118233486</v>
+        <v>0.8380227232169413</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2611,40 +2611,40 @@
         <v>36</v>
       </c>
       <c r="B3">
-        <v>951</v>
+        <v>1469</v>
       </c>
       <c r="C3">
-        <v>674</v>
+        <v>1003</v>
       </c>
       <c r="D3">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="E3">
-        <v>729</v>
+        <v>1116</v>
       </c>
       <c r="F3">
-        <v>205</v>
+        <v>323</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L3" s="1">
-        <v>0.7087276550998949</v>
+        <v>0.6827773995915589</v>
       </c>
       <c r="M3" s="1">
-        <v>0.7665615141955836</v>
+        <v>0.7597004765146358</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2652,19 +2652,19 @@
         <v>37</v>
       </c>
       <c r="B4">
-        <v>1619</v>
+        <v>2625</v>
       </c>
       <c r="C4">
-        <v>935</v>
+        <v>1544</v>
       </c>
       <c r="D4">
-        <v>305</v>
+        <v>450</v>
       </c>
       <c r="E4">
-        <v>1240</v>
+        <v>1994</v>
       </c>
       <c r="F4">
-        <v>346</v>
+        <v>563</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -2673,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2682,10 +2682,10 @@
         <v>1</v>
       </c>
       <c r="L4" s="1">
-        <v>0.5775169857936998</v>
+        <v>0.5881904761904762</v>
       </c>
       <c r="M4" s="1">
-        <v>0.7659048795552811</v>
+        <v>0.7596190476190476</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2693,22 +2693,22 @@
         <v>38</v>
       </c>
       <c r="B5">
-        <v>902</v>
+        <v>1423</v>
       </c>
       <c r="C5">
-        <v>791</v>
+        <v>1235</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>791</v>
+        <v>1235</v>
       </c>
       <c r="F5">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -2723,10 +2723,10 @@
         <v>0</v>
       </c>
       <c r="L5" s="1">
-        <v>0.876940133037694</v>
+        <v>0.8678847505270555</v>
       </c>
       <c r="M5" s="1">
-        <v>0.876940133037694</v>
+        <v>0.8678847505270555</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2734,25 +2734,25 @@
         <v>39</v>
       </c>
       <c r="B6">
-        <v>362</v>
+        <v>538</v>
       </c>
       <c r="C6">
-        <v>314</v>
+        <v>457</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>315</v>
+        <v>458</v>
       </c>
       <c r="F6">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2761,13 +2761,13 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L6" s="1">
-        <v>0.8674033149171271</v>
+        <v>0.8494423791821561</v>
       </c>
       <c r="M6" s="1">
-        <v>0.8701657458563536</v>
+        <v>0.8513011152416357</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2775,40 +2775,40 @@
         <v>40</v>
       </c>
       <c r="B7">
-        <v>834</v>
+        <v>1348</v>
       </c>
       <c r="C7">
-        <v>760</v>
+        <v>1249</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="E7">
-        <v>784</v>
+        <v>1291</v>
       </c>
       <c r="F7">
+        <v>38</v>
+      </c>
+      <c r="G7">
+        <v>16</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>30</v>
       </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>8</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>18</v>
-      </c>
       <c r="L7" s="1">
-        <v>0.9112709832134293</v>
+        <v>0.9265578635014837</v>
       </c>
       <c r="M7" s="1">
-        <v>0.9400479616306955</v>
+        <v>0.9577151335311572</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2816,22 +2816,22 @@
         <v>41</v>
       </c>
       <c r="B8">
-        <v>753</v>
+        <v>1194</v>
       </c>
       <c r="C8">
-        <v>573</v>
+        <v>902</v>
       </c>
       <c r="D8">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="E8">
-        <v>639</v>
+        <v>1005</v>
       </c>
       <c r="F8">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="G8">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -2843,13 +2843,13 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L8" s="1">
-        <v>0.7609561752988048</v>
+        <v>0.7554438860971524</v>
       </c>
       <c r="M8" s="1">
-        <v>0.8486055776892431</v>
+        <v>0.8417085427135679</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2857,19 +2857,19 @@
         <v>42</v>
       </c>
       <c r="B9">
-        <v>773</v>
+        <v>1223</v>
       </c>
       <c r="C9">
-        <v>611</v>
+        <v>920</v>
       </c>
       <c r="D9">
         <v>124</v>
       </c>
       <c r="E9">
-        <v>735</v>
+        <v>1044</v>
       </c>
       <c r="F9">
-        <v>158</v>
+        <v>295</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -2878,19 +2878,19 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="1">
-        <v>0.7904269081500647</v>
+        <v>0.7522485690923958</v>
       </c>
       <c r="M9" s="1">
-        <v>0.9508408796895214</v>
+        <v>0.8536385936222404</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2898,25 +2898,25 @@
         <v>43</v>
       </c>
       <c r="B10">
-        <v>1009</v>
+        <v>1626</v>
       </c>
       <c r="C10">
-        <v>614</v>
+        <v>965</v>
       </c>
       <c r="D10">
-        <v>354</v>
+        <v>586</v>
       </c>
       <c r="E10">
-        <v>968</v>
+        <v>1551</v>
       </c>
       <c r="F10">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -2925,13 +2925,13 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L10" s="1">
-        <v>0.6085232903865213</v>
+        <v>0.593480934809348</v>
       </c>
       <c r="M10" s="1">
-        <v>0.9593657086223984</v>
+        <v>0.9538745387453874</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2939,19 +2939,19 @@
         <v>44</v>
       </c>
       <c r="B11">
-        <v>1013</v>
+        <v>1566</v>
       </c>
       <c r="C11">
-        <v>745</v>
+        <v>1108</v>
       </c>
       <c r="D11">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="E11">
-        <v>775</v>
+        <v>1186</v>
       </c>
       <c r="F11">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -2960,19 +2960,19 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>126</v>
+        <v>222</v>
       </c>
       <c r="L11" s="1">
-        <v>0.7354392892398816</v>
+        <v>0.7075351213282248</v>
       </c>
       <c r="M11" s="1">
-        <v>0.7650542941757157</v>
+        <v>0.7573435504469987</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -2980,19 +2980,19 @@
         <v>45</v>
       </c>
       <c r="B12">
-        <v>525</v>
+        <v>813</v>
       </c>
       <c r="C12">
-        <v>432</v>
+        <v>642</v>
       </c>
       <c r="D12">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="E12">
-        <v>454</v>
+        <v>767</v>
       </c>
       <c r="F12">
-        <v>149</v>
+        <v>244</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -3007,13 +3007,13 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="1">
-        <v>0.8228571428571428</v>
+        <v>0.7896678966789668</v>
       </c>
       <c r="M12" s="1">
-        <v>0.8647619047619047</v>
+        <v>0.9434194341943419</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -3021,19 +3021,19 @@
         <v>46</v>
       </c>
       <c r="B13">
-        <v>168</v>
+        <v>292</v>
       </c>
       <c r="C13">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="D13">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="E13">
-        <v>125</v>
+        <v>221</v>
       </c>
       <c r="F13">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -3051,10 +3051,10 @@
         <v>0</v>
       </c>
       <c r="L13" s="1">
-        <v>0.375</v>
+        <v>0.3938356164383562</v>
       </c>
       <c r="M13" s="1">
-        <v>0.7440476190476191</v>
+        <v>0.7568493150684932</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -3062,19 +3062,19 @@
         <v>47</v>
       </c>
       <c r="B14">
-        <v>427</v>
+        <v>660</v>
       </c>
       <c r="C14">
-        <v>351</v>
+        <v>514</v>
       </c>
       <c r="D14">
         <v>45</v>
       </c>
       <c r="E14">
-        <v>396</v>
+        <v>559</v>
       </c>
       <c r="F14">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3092,10 +3092,10 @@
         <v>0</v>
       </c>
       <c r="L14" s="1">
-        <v>0.8220140515222483</v>
+        <v>0.7787878787878788</v>
       </c>
       <c r="M14" s="1">
-        <v>0.927400468384075</v>
+        <v>0.8469696969696969</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -3103,19 +3103,19 @@
         <v>48</v>
       </c>
       <c r="B15">
-        <v>357</v>
+        <v>548</v>
       </c>
       <c r="C15">
-        <v>345</v>
+        <v>509</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E15">
-        <v>345</v>
+        <v>520</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -3133,10 +3133,10 @@
         <v>0</v>
       </c>
       <c r="L15" s="1">
-        <v>0.9663865546218487</v>
+        <v>0.9288321167883211</v>
       </c>
       <c r="M15" s="1">
-        <v>0.9663865546218487</v>
+        <v>0.948905109489051</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -3144,40 +3144,40 @@
         <v>49</v>
       </c>
       <c r="B16">
-        <v>741</v>
+        <v>1009</v>
       </c>
       <c r="C16">
-        <v>378</v>
+        <v>510</v>
       </c>
       <c r="D16">
-        <v>137</v>
+        <v>183</v>
       </c>
       <c r="E16">
-        <v>515</v>
+        <v>693</v>
       </c>
       <c r="F16">
-        <v>139</v>
+        <v>207</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="L16" s="1">
-        <v>0.5101214574898786</v>
+        <v>0.5054509415262636</v>
       </c>
       <c r="M16" s="1">
-        <v>0.6950067476383266</v>
+        <v>0.686818632309217</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -3185,22 +3185,22 @@
         <v>50</v>
       </c>
       <c r="B17">
-        <v>275</v>
+        <v>431</v>
       </c>
       <c r="C17">
-        <v>239</v>
+        <v>381</v>
       </c>
       <c r="D17">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E17">
-        <v>255</v>
+        <v>404</v>
       </c>
       <c r="F17">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17">
         <v>2</v>
@@ -3215,10 +3215,10 @@
         <v>0</v>
       </c>
       <c r="L17" s="1">
-        <v>0.8690909090909091</v>
+        <v>0.8839907192575406</v>
       </c>
       <c r="M17" s="1">
-        <v>0.9272727272727272</v>
+        <v>0.9373549883990719</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -3226,19 +3226,19 @@
         <v>51</v>
       </c>
       <c r="B18">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C18">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3256,10 +3256,10 @@
         <v>0</v>
       </c>
       <c r="L18" s="1">
-        <v>0.9583333333333334</v>
+        <v>0.9130434782608695</v>
       </c>
       <c r="M18" s="1">
-        <v>1</v>
+        <v>0.9565217391304348</v>
       </c>
     </row>
   </sheetData>
@@ -3321,40 +3321,40 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>2901</v>
+        <v>4701</v>
       </c>
       <c r="C2">
-        <v>86</v>
+        <v>163</v>
       </c>
       <c r="D2">
-        <v>823</v>
+        <v>1377</v>
       </c>
       <c r="E2">
-        <v>909</v>
+        <v>1540</v>
       </c>
       <c r="F2">
-        <v>1692</v>
+        <v>2735</v>
       </c>
       <c r="G2">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="H2">
-        <v>173</v>
+        <v>257</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L2" s="1">
-        <v>0.02964495001723544</v>
+        <v>0.03467347372899383</v>
       </c>
       <c r="M2" s="1">
-        <v>0.3133402275077559</v>
+        <v>0.3275898744947883</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3362,19 +3362,19 @@
         <v>36</v>
       </c>
       <c r="B3">
-        <v>424</v>
+        <v>708</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>151</v>
+        <v>306</v>
       </c>
       <c r="E3">
-        <v>151</v>
+        <v>306</v>
       </c>
       <c r="F3">
-        <v>210</v>
+        <v>292</v>
       </c>
       <c r="G3">
         <v>7</v>
@@ -3383,7 +3383,7 @@
         <v>7</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -3395,7 +3395,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="1">
-        <v>0.3561320754716981</v>
+        <v>0.4322033898305085</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3403,28 +3403,28 @@
         <v>37</v>
       </c>
       <c r="B4">
-        <v>424</v>
+        <v>677</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>152</v>
+        <v>230</v>
       </c>
       <c r="E4">
-        <v>153</v>
+        <v>232</v>
       </c>
       <c r="F4">
-        <v>233</v>
+        <v>387</v>
       </c>
       <c r="G4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H4">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3433,10 +3433,10 @@
         <v>1</v>
       </c>
       <c r="L4" s="1">
-        <v>0.002358490566037736</v>
+        <v>0.002954209748892172</v>
       </c>
       <c r="M4" s="1">
-        <v>0.3608490566037736</v>
+        <v>0.3426883308714919</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -3479,19 +3479,19 @@
         <v>39</v>
       </c>
       <c r="B6">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -3512,7 +3512,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>0.1282051282051282</v>
+        <v>0.1578947368421053</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3520,40 +3520,40 @@
         <v>40</v>
       </c>
       <c r="B7">
-        <v>199</v>
+        <v>359</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F7">
-        <v>150</v>
+        <v>261</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H7">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" s="1">
-        <v>0</v>
+        <v>0.008356545961002786</v>
       </c>
       <c r="M7" s="1">
-        <v>0.06532663316582915</v>
+        <v>0.0584958217270195</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -3561,25 +3561,25 @@
         <v>41</v>
       </c>
       <c r="B8">
-        <v>198</v>
+        <v>344</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E8">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F8">
-        <v>147</v>
+        <v>272</v>
       </c>
       <c r="G8">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -3594,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="1">
-        <v>0.1868686868686869</v>
+        <v>0.1279069767441861</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3602,25 +3602,25 @@
         <v>42</v>
       </c>
       <c r="B9">
-        <v>165</v>
+        <v>244</v>
       </c>
       <c r="C9">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D9">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="E9">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="F9">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H9">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -3632,10 +3632,10 @@
         <v>4</v>
       </c>
       <c r="L9" s="1">
-        <v>0.1575757575757576</v>
+        <v>0.2172131147540984</v>
       </c>
       <c r="M9" s="1">
-        <v>0.5757575757575758</v>
+        <v>0.610655737704918</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -3643,28 +3643,28 @@
         <v>43</v>
       </c>
       <c r="B10">
-        <v>257</v>
+        <v>405</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="E10">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="F10">
-        <v>143</v>
+        <v>233</v>
       </c>
       <c r="G10">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H10">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3676,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="1">
-        <v>0.3035019455252918</v>
+        <v>0.2814814814814815</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3684,25 +3684,25 @@
         <v>44</v>
       </c>
       <c r="B11">
-        <v>380</v>
+        <v>616</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D11">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="E11">
-        <v>96</v>
+        <v>151</v>
       </c>
       <c r="F11">
-        <v>267</v>
+        <v>441</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -3714,10 +3714,10 @@
         <v>0</v>
       </c>
       <c r="L11" s="1">
-        <v>0.03947368421052631</v>
+        <v>0.03733766233766234</v>
       </c>
       <c r="M11" s="1">
-        <v>0.2526315789473684</v>
+        <v>0.2451298701298701</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -3725,25 +3725,25 @@
         <v>45</v>
       </c>
       <c r="B12">
-        <v>229</v>
+        <v>374</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D12">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E12">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F12">
-        <v>194</v>
+        <v>320</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -3755,10 +3755,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="1">
-        <v>0.02183406113537118</v>
+        <v>0.03208556149732621</v>
       </c>
       <c r="M12" s="1">
-        <v>0.06550218340611354</v>
+        <v>0.08021390374331551</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -3766,40 +3766,40 @@
         <v>46</v>
       </c>
       <c r="B13">
-        <v>239</v>
+        <v>385</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="D13">
-        <v>124</v>
+        <v>215</v>
       </c>
       <c r="E13">
-        <v>126</v>
+        <v>217</v>
       </c>
       <c r="F13">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L13" s="1">
-        <v>0.008368200836820083</v>
+        <v>0.005194805194805195</v>
       </c>
       <c r="M13" s="1">
-        <v>0.5271966527196653</v>
+        <v>0.5636363636363636</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -3807,20 +3807,20 @@
         <v>47</v>
       </c>
       <c r="B14">
+        <v>55</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>64</v>
+      </c>
+      <c r="E14">
+        <v>64</v>
+      </c>
+      <c r="F14">
         <v>27</v>
       </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>11</v>
-      </c>
-      <c r="E14">
-        <v>11</v>
-      </c>
-      <c r="F14">
-        <v>11</v>
-      </c>
       <c r="G14">
         <v>1</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="1">
-        <v>0.4074074074074074</v>
+        <v>1.163636363636364</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -3848,22 +3848,22 @@
         <v>48</v>
       </c>
       <c r="B15">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="C15">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D15">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="E15">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="F15">
+        <v>5</v>
+      </c>
+      <c r="G15">
         <v>4</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
       </c>
       <c r="H15">
         <v>5</v>
@@ -3878,10 +3878,10 @@
         <v>0</v>
       </c>
       <c r="L15" s="1">
-        <v>0.358695652173913</v>
+        <v>0.4068965517241379</v>
       </c>
       <c r="M15" s="1">
-        <v>0.9565217391304348</v>
+        <v>0.8896551724137931</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -3889,28 +3889,28 @@
         <v>49</v>
       </c>
       <c r="B16">
-        <v>178</v>
+        <v>244</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E16">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F16">
-        <v>133</v>
+        <v>180</v>
       </c>
       <c r="G16">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="H16">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3922,7 +3922,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="1">
-        <v>0.1292134831460674</v>
+        <v>0.1516393442622951</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -3930,25 +3930,25 @@
         <v>50</v>
       </c>
       <c r="B17">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D17">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E17">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F17">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -3960,10 +3960,10 @@
         <v>0</v>
       </c>
       <c r="L17" s="1">
-        <v>0.08</v>
+        <v>0.1022727272727273</v>
       </c>
       <c r="M17" s="1">
-        <v>0.36</v>
+        <v>0.4204545454545455</v>
       </c>
     </row>
     <row r="18" spans="1:13">
